--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.68</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="B2">
-        <v>0.02173913043478261</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5704225352112676</v>
+        <v>0.4577464788732394</v>
       </c>
       <c r="D2">
-        <v>0.6354166666666666</v>
+        <v>0.5968992248062015</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="F2">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="G2">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8387096774193549</v>
+        <v>0.8360655737704918</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4577464788732394</v>
+        <v>0.4718309859154929</v>
       </c>
       <c r="D2">
-        <v>0.5968992248062015</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="E2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
